--- a/pyrate_features_binning/model_9_offset_syn_new_pyrate_features.xlsx
+++ b/pyrate_features_binning/model_9_offset_syn_new_pyrate_features.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimoesLabAdmin\Documents\pt_diversity_rates\pyrate_features_binning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECB7A368-288B-42BF-9417-D82BA12DEA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2721D210-CB54-4E48-B28E-84AC55178642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57975" yWindow="645" windowWidth="28440" windowHeight="12435" xr2:uid="{5A31E4FE-E537-4CDD-8621-3B98C98941C8}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5A31E4FE-E537-4CDD-8621-3B98C98941C8}"/>
   </bookViews>
   <sheets>
     <sheet name="new_pyrate_features" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="28">
   <si>
     <t>mat_z_trans</t>
   </si>
@@ -85,6 +96,30 @@
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>Asselian</t>
+  </si>
+  <si>
+    <t>Sakmarian</t>
+  </si>
+  <si>
+    <t>Artinskian</t>
+  </si>
+  <si>
+    <t>Kungurian</t>
+  </si>
+  <si>
+    <t>Roadian</t>
+  </si>
+  <si>
+    <t>Wordian</t>
+  </si>
+  <si>
+    <t>Capit</t>
   </si>
 </sst>
 </file>
@@ -227,7 +262,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,6 +448,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -574,10 +615,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -953,10 +996,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F0D798-CCFF-4ADA-A203-6DC93CF0F7C9}">
-  <dimension ref="A1:AA109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
       <c r="G1" t="s">
         <v>0</v>
       </c>
@@ -1017,8 +1060,11 @@
       <c r="AA1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -1101,8 +1147,11 @@
         <f>Z2+174.5</f>
         <v>297.64636993408203</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -1185,8 +1234,11 @@
         <f t="shared" ref="AA3:AA66" si="0">Z3+174.5</f>
         <v>297</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -1269,8 +1321,11 @@
         <f t="shared" si="0"/>
         <v>296</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -1353,8 +1408,11 @@
         <f t="shared" si="0"/>
         <v>295</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -1437,344 +1495,359 @@
         <f t="shared" si="0"/>
         <v>294</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A7" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="AB6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A7" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
         <v>1.0699664354324301</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="3">
         <v>-1.022754073143</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="3">
         <v>-0.16037909686565299</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="3">
         <v>1.1551251411437899</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="3">
         <v>-1.00714588165283</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="3">
         <v>-0.85971987247466997</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7" s="3">
         <v>-1.0408400297164899</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="3">
         <v>-0.40474414825439398</v>
       </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>0</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="1">
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3">
         <v>118.5</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="4">
         <f t="shared" si="0"/>
         <v>293</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A8" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="AB7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A8" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>1.0045018196105899</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="3">
         <v>-0.86818528175354004</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="3">
         <v>-0.22135348618030501</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="3">
         <v>1.10611879825592</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="3">
         <v>-0.993419349193572</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8" s="3">
         <v>-0.657032251358032</v>
       </c>
-      <c r="M8" s="1">
+      <c r="M8" s="3">
         <v>-1.03426301479339</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8" s="3">
         <v>-0.13539518415927801</v>
       </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
-      <c r="T8" s="1">
-        <v>0</v>
-      </c>
-      <c r="U8" s="1">
-        <v>0</v>
-      </c>
-      <c r="V8" s="1">
-        <v>0</v>
-      </c>
-      <c r="W8" s="1">
-        <v>0</v>
-      </c>
-      <c r="X8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="1">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>117.5</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="4">
         <f t="shared" si="0"/>
         <v>292</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A9" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="AB8" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A9" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
         <v>1.0045018196105899</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="3">
         <v>-0.86818528175354004</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="3">
         <v>-0.22135348618030501</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="3">
         <v>1.10611879825592</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="3">
         <v>-0.993419349193572</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="3">
         <v>-0.657032251358032</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="3">
         <v>-1.03426301479339</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="3">
         <v>-0.13539518415927801</v>
       </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="1">
-        <v>0</v>
-      </c>
-      <c r="U9" s="1">
-        <v>0</v>
-      </c>
-      <c r="V9" s="1">
-        <v>0</v>
-      </c>
-      <c r="W9" s="1">
-        <v>0</v>
-      </c>
-      <c r="X9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="1">
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3">
         <v>116.5</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="4">
         <f t="shared" si="0"/>
         <v>291</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A10" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="AB9" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A10" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>1.0045018196105899</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="3">
         <v>-0.86818528175354004</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="3">
         <v>-0.22135348618030501</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="3">
         <v>1.10611879825592</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10" s="3">
         <v>-0.993419349193572</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10" s="3">
         <v>-0.657032251358032</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M10" s="3">
         <v>-1.03426301479339</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="3">
         <v>-0.13539518415927801</v>
       </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="1">
-        <v>0</v>
-      </c>
-      <c r="U10" s="1">
-        <v>0</v>
-      </c>
-      <c r="V10" s="1">
-        <v>0</v>
-      </c>
-      <c r="W10" s="1">
-        <v>0</v>
-      </c>
-      <c r="X10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="2">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="1">
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="3">
         <v>115.550003051757</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="4">
         <f t="shared" si="0"/>
         <v>290.05000305175702</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB10" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -1857,8 +1930,11 @@
         <f t="shared" si="0"/>
         <v>289.55000305175702</v>
       </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -1941,8 +2017,11 @@
         <f t="shared" si="0"/>
         <v>289</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -2025,8 +2104,11 @@
         <f t="shared" si="0"/>
         <v>288</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -2109,8 +2191,11 @@
         <f t="shared" si="0"/>
         <v>287</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -2193,8 +2278,11 @@
         <f t="shared" si="0"/>
         <v>286</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -2277,8 +2365,11 @@
         <f t="shared" si="0"/>
         <v>285</v>
       </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -2361,8 +2452,11 @@
         <f t="shared" si="0"/>
         <v>284</v>
       </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -2445,1016 +2539,1055 @@
         <f t="shared" si="0"/>
         <v>283.25</v>
       </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A19" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
+      <c r="AB18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A19" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M19" s="1">
+      <c r="M19" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N19" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O19" s="1">
-        <v>0</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1">
-        <v>0</v>
-      </c>
-      <c r="S19" s="1">
-        <v>0</v>
-      </c>
-      <c r="T19" s="1">
-        <v>0</v>
-      </c>
-      <c r="U19" s="1">
-        <v>0</v>
-      </c>
-      <c r="V19" s="1">
-        <v>0</v>
-      </c>
-      <c r="W19" s="1">
-        <v>0</v>
-      </c>
-      <c r="X19" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="1">
+      <c r="O19" s="3">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3">
+        <v>0</v>
+      </c>
+      <c r="T19" s="3">
+        <v>0</v>
+      </c>
+      <c r="U19" s="3">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3">
+        <v>0</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="3">
         <v>108.25</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="4">
         <f t="shared" si="0"/>
         <v>282.75</v>
       </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A20" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
+      <c r="AB19" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A20" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M20" s="1">
+      <c r="M20" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>0</v>
-      </c>
-      <c r="R20" s="1">
-        <v>0</v>
-      </c>
-      <c r="S20" s="1">
-        <v>0</v>
-      </c>
-      <c r="T20" s="1">
-        <v>0</v>
-      </c>
-      <c r="U20" s="1">
-        <v>0</v>
-      </c>
-      <c r="V20" s="1">
-        <v>0</v>
-      </c>
-      <c r="W20" s="1">
-        <v>0</v>
-      </c>
-      <c r="X20" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="1">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>107.5</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="4">
         <f t="shared" si="0"/>
         <v>282</v>
       </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A21" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
+      <c r="AB20" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A21" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M21" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N21" s="1">
+      <c r="N21" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>0</v>
-      </c>
-      <c r="T21" s="1">
-        <v>0</v>
-      </c>
-      <c r="U21" s="1">
-        <v>0</v>
-      </c>
-      <c r="V21" s="1">
-        <v>0</v>
-      </c>
-      <c r="W21" s="1">
-        <v>0</v>
-      </c>
-      <c r="X21" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="1">
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
         <v>106.5</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" s="4">
         <f t="shared" si="0"/>
         <v>281</v>
       </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A22" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
+      <c r="AB21" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A22" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M22" s="1">
+      <c r="M22" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N22" s="1">
+      <c r="N22" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-      <c r="P22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>0</v>
-      </c>
-      <c r="R22" s="1">
-        <v>0</v>
-      </c>
-      <c r="S22" s="1">
-        <v>0</v>
-      </c>
-      <c r="T22" s="1">
-        <v>0</v>
-      </c>
-      <c r="U22" s="1">
-        <v>0</v>
-      </c>
-      <c r="V22" s="1">
-        <v>0</v>
-      </c>
-      <c r="W22" s="1">
-        <v>0</v>
-      </c>
-      <c r="X22" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="1">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>105.5</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="4">
         <f t="shared" si="0"/>
         <v>280</v>
       </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A23" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
+      <c r="AB22" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A23" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M23" s="1">
+      <c r="M23" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>0</v>
-      </c>
-      <c r="R23" s="1">
-        <v>0</v>
-      </c>
-      <c r="S23" s="1">
-        <v>0</v>
-      </c>
-      <c r="T23" s="1">
-        <v>0</v>
-      </c>
-      <c r="U23" s="1">
-        <v>0</v>
-      </c>
-      <c r="V23" s="1">
-        <v>0</v>
-      </c>
-      <c r="W23" s="1">
-        <v>0</v>
-      </c>
-      <c r="X23" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="1">
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
         <v>104.5</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="4">
         <f t="shared" si="0"/>
         <v>279</v>
       </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A24" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
+      <c r="AB23" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A24" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K24" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L24" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M24" s="1">
+      <c r="M24" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N24" s="1">
+      <c r="N24" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O24" s="1">
-        <v>0</v>
-      </c>
-      <c r="P24" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>0</v>
-      </c>
-      <c r="R24" s="1">
-        <v>0</v>
-      </c>
-      <c r="S24" s="1">
-        <v>0</v>
-      </c>
-      <c r="T24" s="1">
-        <v>0</v>
-      </c>
-      <c r="U24" s="1">
-        <v>0</v>
-      </c>
-      <c r="V24" s="1">
-        <v>0</v>
-      </c>
-      <c r="W24" s="1">
-        <v>0</v>
-      </c>
-      <c r="X24" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="1">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>103.5</v>
       </c>
-      <c r="AA24">
+      <c r="AA24" s="4">
         <f t="shared" si="0"/>
         <v>278</v>
       </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A25" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
+      <c r="AB24" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A25" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K25" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L25" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M25" s="1">
+      <c r="M25" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N25" s="1">
+      <c r="N25" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>0</v>
-      </c>
-      <c r="R25" s="1">
-        <v>0</v>
-      </c>
-      <c r="S25" s="1">
-        <v>0</v>
-      </c>
-      <c r="T25" s="1">
-        <v>0</v>
-      </c>
-      <c r="U25" s="1">
-        <v>0</v>
-      </c>
-      <c r="V25" s="1">
-        <v>0</v>
-      </c>
-      <c r="W25" s="1">
-        <v>0</v>
-      </c>
-      <c r="X25" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="1">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
         <v>102.5</v>
       </c>
-      <c r="AA25">
+      <c r="AA25" s="4">
         <f t="shared" si="0"/>
         <v>277</v>
       </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A26" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
+      <c r="AB25" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A26" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K26" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L26" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M26" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O26" s="1">
-        <v>0</v>
-      </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>0</v>
-      </c>
-      <c r="R26" s="1">
-        <v>0</v>
-      </c>
-      <c r="S26" s="1">
-        <v>0</v>
-      </c>
-      <c r="T26" s="1">
-        <v>0</v>
-      </c>
-      <c r="U26" s="1">
-        <v>0</v>
-      </c>
-      <c r="V26" s="1">
-        <v>0</v>
-      </c>
-      <c r="W26" s="1">
-        <v>0</v>
-      </c>
-      <c r="X26" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="1">
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>101.5</v>
       </c>
-      <c r="AA26">
+      <c r="AA26" s="4">
         <f t="shared" si="0"/>
         <v>276</v>
       </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A27" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B27" s="1">
-        <v>0</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1">
+      <c r="AB26" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A27" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K27" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L27" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M27" s="1">
+      <c r="M27" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N27" s="1">
+      <c r="N27" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O27" s="1">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
-      <c r="S27" s="1">
-        <v>0</v>
-      </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
-      <c r="U27" s="1">
-        <v>0</v>
-      </c>
-      <c r="V27" s="1">
-        <v>0</v>
-      </c>
-      <c r="W27" s="1">
-        <v>0</v>
-      </c>
-      <c r="X27" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="1">
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>100.5</v>
       </c>
-      <c r="AA27">
+      <c r="AA27" s="4">
         <f t="shared" si="0"/>
         <v>275</v>
       </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A28" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1">
+      <c r="AB27" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A28" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B28" s="3">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K28" s="1">
+      <c r="K28" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L28" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M28" s="1">
+      <c r="M28" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N28" s="1">
+      <c r="N28" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O28" s="1">
-        <v>0</v>
-      </c>
-      <c r="P28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="1">
-        <v>0</v>
-      </c>
-      <c r="R28" s="1">
-        <v>0</v>
-      </c>
-      <c r="S28" s="1">
-        <v>0</v>
-      </c>
-      <c r="T28" s="1">
-        <v>0</v>
-      </c>
-      <c r="U28" s="1">
-        <v>0</v>
-      </c>
-      <c r="V28" s="1">
-        <v>0</v>
-      </c>
-      <c r="W28" s="2">
-        <v>1</v>
-      </c>
-      <c r="X28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="1">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>1</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
         <v>99.699996948242102</v>
       </c>
-      <c r="AA28">
+      <c r="AA28" s="4">
         <f t="shared" si="0"/>
         <v>274.19999694824207</v>
       </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A29" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1">
+      <c r="AB28" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A29" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K29" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L29" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M29" s="1">
+      <c r="M29" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N29" s="1">
+      <c r="N29" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O29" s="1">
-        <v>0</v>
-      </c>
-      <c r="P29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="1">
-        <v>0</v>
-      </c>
-      <c r="R29" s="1">
-        <v>0</v>
-      </c>
-      <c r="S29" s="1">
-        <v>0</v>
-      </c>
-      <c r="T29" s="1">
-        <v>0</v>
-      </c>
-      <c r="U29" s="1">
-        <v>0</v>
-      </c>
-      <c r="V29" s="1">
-        <v>0</v>
-      </c>
-      <c r="W29" s="2">
-        <v>1</v>
-      </c>
-      <c r="X29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="1">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>1</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>99.199996948242102</v>
       </c>
-      <c r="AA29">
+      <c r="AA29" s="4">
         <f t="shared" si="0"/>
         <v>273.69999694824207</v>
       </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A30" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
-        <v>0</v>
-      </c>
-      <c r="G30" s="1">
+      <c r="AB29" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A30" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B30" s="3">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3">
         <v>1.22034168243408</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="3">
         <v>-1.04577696323394</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="3">
         <v>2.1844444796442899E-2</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="3">
         <v>1.21827244758605</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K30" s="3">
         <v>-0.98048037290573098</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30" s="3">
         <v>-0.64512234926223699</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M30" s="3">
         <v>-1.06577825546264</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="3">
         <v>-9.6334323287010096E-2</v>
       </c>
-      <c r="O30" s="1">
-        <v>0</v>
-      </c>
-      <c r="P30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="1">
-        <v>0</v>
-      </c>
-      <c r="R30" s="1">
-        <v>0</v>
-      </c>
-      <c r="S30" s="1">
-        <v>0</v>
-      </c>
-      <c r="T30" s="1">
-        <v>0</v>
-      </c>
-      <c r="U30" s="1">
-        <v>0</v>
-      </c>
-      <c r="V30" s="1">
-        <v>0</v>
-      </c>
-      <c r="W30" s="2">
-        <v>1</v>
-      </c>
-      <c r="X30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="1">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>1</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
         <v>98.5</v>
       </c>
-      <c r="AA30">
+      <c r="AA30" s="4">
         <f t="shared" si="0"/>
         <v>273</v>
       </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB30" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -3537,8 +3670,11 @@
         <f t="shared" si="0"/>
         <v>272</v>
       </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -3621,8 +3757,11 @@
         <f t="shared" si="0"/>
         <v>271</v>
       </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -3705,8 +3844,11 @@
         <f t="shared" si="0"/>
         <v>270</v>
       </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -3789,512 +3931,533 @@
         <f t="shared" si="0"/>
         <v>269</v>
       </c>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A35" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0</v>
-      </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1">
+      <c r="AB34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A35" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-0.242348387837409</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="3">
         <v>1.51181328296661</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I35" s="3">
         <v>-1.3973786830902</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="3">
         <v>0.39136418700218201</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K35" s="3">
         <v>-0.91590207815170199</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L35" s="3">
         <v>0.71323215961456199</v>
       </c>
-      <c r="M35" s="1">
+      <c r="M35" s="3">
         <v>2.1198363304138099</v>
       </c>
-      <c r="N35" s="1">
+      <c r="N35" s="3">
         <v>-0.57921659946441595</v>
       </c>
-      <c r="O35" s="1">
-        <v>0</v>
-      </c>
-      <c r="P35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>0</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1">
-        <v>0</v>
-      </c>
-      <c r="T35" s="1">
-        <v>0</v>
-      </c>
-      <c r="U35" s="1">
-        <v>0</v>
-      </c>
-      <c r="V35" s="1">
-        <v>0</v>
-      </c>
-      <c r="W35" s="2">
-        <v>1</v>
-      </c>
-      <c r="X35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="1">
+      <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
+        <v>1</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>93.5</v>
       </c>
-      <c r="AA35">
+      <c r="AA35" s="4">
         <f t="shared" si="0"/>
         <v>268</v>
       </c>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A36" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0</v>
-      </c>
-      <c r="E36" s="1">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1">
+      <c r="AB35" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A36" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B36" s="3">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3">
         <v>-0.720370233058929</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="3">
         <v>1.9656730890273999</v>
       </c>
-      <c r="I36" s="1">
+      <c r="I36" s="3">
         <v>-2.0693712234496999</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="3">
         <v>0.218691110610961</v>
       </c>
-      <c r="K36" s="1">
+      <c r="K36" s="3">
         <v>-1.0631469488143901</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L36" s="3">
         <v>1.08242082595825</v>
       </c>
-      <c r="M36" s="1">
+      <c r="M36" s="3">
         <v>2.8652558326721098</v>
       </c>
-      <c r="N36" s="1">
+      <c r="N36" s="3">
         <v>-0.62277072668075495</v>
       </c>
-      <c r="O36" s="1">
-        <v>0</v>
-      </c>
-      <c r="P36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>0</v>
-      </c>
-      <c r="R36" s="1">
-        <v>0</v>
-      </c>
-      <c r="S36" s="1">
-        <v>0</v>
-      </c>
-      <c r="T36" s="1">
-        <v>0</v>
-      </c>
-      <c r="U36" s="1">
-        <v>0</v>
-      </c>
-      <c r="V36" s="1">
-        <v>0</v>
-      </c>
-      <c r="W36" s="2">
-        <v>1</v>
-      </c>
-      <c r="X36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="1">
+      <c r="O36" s="3">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>0</v>
+      </c>
+      <c r="R36" s="3">
+        <v>0</v>
+      </c>
+      <c r="S36" s="3">
+        <v>0</v>
+      </c>
+      <c r="T36" s="3">
+        <v>0</v>
+      </c>
+      <c r="U36" s="3">
+        <v>0</v>
+      </c>
+      <c r="V36" s="3">
+        <v>0</v>
+      </c>
+      <c r="W36" s="3">
+        <v>1</v>
+      </c>
+      <c r="X36" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="3">
         <v>92.5</v>
       </c>
-      <c r="AA36">
+      <c r="AA36" s="4">
         <f t="shared" si="0"/>
         <v>267</v>
       </c>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A37" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0</v>
-      </c>
-      <c r="C37" s="1">
-        <v>0</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
+      <c r="AB36" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A37" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B37" s="3">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3">
         <v>-0.720370233058929</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="3">
         <v>1.9656730890273999</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37" s="3">
         <v>-2.0693712234496999</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="3">
         <v>0.218691110610961</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K37" s="3">
         <v>-1.0631469488143901</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L37" s="3">
         <v>1.08242082595825</v>
       </c>
-      <c r="M37" s="1">
+      <c r="M37" s="3">
         <v>2.8652558326721098</v>
       </c>
-      <c r="N37" s="1">
+      <c r="N37" s="3">
         <v>-0.62277072668075495</v>
       </c>
-      <c r="O37" s="1">
-        <v>0</v>
-      </c>
-      <c r="P37" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>0</v>
-      </c>
-      <c r="R37" s="1">
-        <v>0</v>
-      </c>
-      <c r="S37" s="1">
-        <v>0</v>
-      </c>
-      <c r="T37" s="1">
-        <v>0</v>
-      </c>
-      <c r="U37" s="1">
-        <v>0</v>
-      </c>
-      <c r="V37" s="1">
-        <v>0</v>
-      </c>
-      <c r="W37" s="2">
-        <v>1</v>
-      </c>
-      <c r="X37" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="1">
+      <c r="O37" s="3">
+        <v>0</v>
+      </c>
+      <c r="P37" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>0</v>
+      </c>
+      <c r="R37" s="3">
+        <v>0</v>
+      </c>
+      <c r="S37" s="3">
+        <v>0</v>
+      </c>
+      <c r="T37" s="3">
+        <v>0</v>
+      </c>
+      <c r="U37" s="3">
+        <v>0</v>
+      </c>
+      <c r="V37" s="3">
+        <v>0</v>
+      </c>
+      <c r="W37" s="3">
+        <v>1</v>
+      </c>
+      <c r="X37" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="3">
         <v>91.5</v>
       </c>
-      <c r="AA37">
+      <c r="AA37" s="4">
         <f t="shared" si="0"/>
         <v>266</v>
       </c>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A38" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0</v>
-      </c>
-      <c r="C38" s="1">
-        <v>0</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
+      <c r="AB37" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A38" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B38" s="3">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3">
         <v>-0.720370233058929</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="3">
         <v>1.9656730890273999</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I38" s="3">
         <v>-2.0693712234496999</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="3">
         <v>0.218691110610961</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K38" s="3">
         <v>-1.0631469488143901</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L38" s="3">
         <v>1.08242082595825</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M38" s="3">
         <v>2.8652558326721098</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N38" s="3">
         <v>-0.62277072668075495</v>
       </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
-      <c r="P38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>0</v>
-      </c>
-      <c r="R38" s="1">
-        <v>0</v>
-      </c>
-      <c r="S38" s="1">
-        <v>0</v>
-      </c>
-      <c r="T38" s="1">
-        <v>0</v>
-      </c>
-      <c r="U38" s="1">
-        <v>0</v>
-      </c>
-      <c r="V38" s="1">
-        <v>0</v>
-      </c>
-      <c r="W38" s="2">
-        <v>1</v>
-      </c>
-      <c r="X38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="1">
+      <c r="O38" s="3">
+        <v>0</v>
+      </c>
+      <c r="P38" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>0</v>
+      </c>
+      <c r="R38" s="3">
+        <v>0</v>
+      </c>
+      <c r="S38" s="3">
+        <v>0</v>
+      </c>
+      <c r="T38" s="3">
+        <v>0</v>
+      </c>
+      <c r="U38" s="3">
+        <v>0</v>
+      </c>
+      <c r="V38" s="3">
+        <v>0</v>
+      </c>
+      <c r="W38" s="3">
+        <v>1</v>
+      </c>
+      <c r="X38" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="3">
         <v>90.5</v>
       </c>
-      <c r="AA38">
+      <c r="AA38" s="4">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A39" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1</v>
-      </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
+      <c r="AB38" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A39" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B39" s="3">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
         <v>-0.720370233058929</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="3">
         <v>1.9656730890273999</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I39" s="3">
         <v>-2.0693712234496999</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="3">
         <v>0.218691110610961</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K39" s="3">
         <v>-1.0631469488143901</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L39" s="3">
         <v>1.08242082595825</v>
       </c>
-      <c r="M39" s="1">
+      <c r="M39" s="3">
         <v>2.8652558326721098</v>
       </c>
-      <c r="N39" s="1">
+      <c r="N39" s="3">
         <v>-0.62277072668075495</v>
       </c>
-      <c r="O39" s="1">
-        <v>0</v>
-      </c>
-      <c r="P39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>0</v>
-      </c>
-      <c r="R39" s="1">
-        <v>0</v>
-      </c>
-      <c r="S39" s="1">
-        <v>0</v>
-      </c>
-      <c r="T39" s="1">
-        <v>0</v>
-      </c>
-      <c r="U39" s="1">
-        <v>0</v>
-      </c>
-      <c r="V39" s="2">
-        <v>1</v>
-      </c>
-      <c r="W39" s="1">
-        <v>0</v>
-      </c>
-      <c r="X39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="1">
+      <c r="O39" s="3">
+        <v>0</v>
+      </c>
+      <c r="P39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>0</v>
+      </c>
+      <c r="R39" s="3">
+        <v>0</v>
+      </c>
+      <c r="S39" s="3">
+        <v>0</v>
+      </c>
+      <c r="T39" s="3">
+        <v>0</v>
+      </c>
+      <c r="U39" s="3">
+        <v>0</v>
+      </c>
+      <c r="V39" s="3">
+        <v>1</v>
+      </c>
+      <c r="W39" s="3">
+        <v>0</v>
+      </c>
+      <c r="X39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="3">
         <v>89.650001525878906</v>
       </c>
-      <c r="AA39">
+      <c r="AA39" s="4">
         <f t="shared" si="0"/>
         <v>264.15000152587891</v>
       </c>
-    </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A40" s="1">
-        <v>-0.29742455482482899</v>
-      </c>
-      <c r="B40" s="1">
-        <v>0</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0</v>
-      </c>
-      <c r="E40" s="1">
-        <v>1</v>
-      </c>
-      <c r="F40" s="1">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1">
+      <c r="AB39" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A40" s="3">
+        <v>-0.29742455482482899</v>
+      </c>
+      <c r="B40" s="3">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
         <v>-0.720370233058929</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="3">
         <v>1.9656730890273999</v>
       </c>
-      <c r="I40" s="1">
+      <c r="I40" s="3">
         <v>-2.0693712234496999</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="3">
         <v>0.218691110610961</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K40" s="3">
         <v>-1.0631469488143901</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L40" s="3">
         <v>1.08242082595825</v>
       </c>
-      <c r="M40" s="1">
+      <c r="M40" s="3">
         <v>2.8652558326721098</v>
       </c>
-      <c r="N40" s="1">
+      <c r="N40" s="3">
         <v>-0.62277072668075495</v>
       </c>
-      <c r="O40" s="1">
-        <v>0</v>
-      </c>
-      <c r="P40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>0</v>
-      </c>
-      <c r="R40" s="1">
-        <v>0</v>
-      </c>
-      <c r="S40" s="1">
-        <v>0</v>
-      </c>
-      <c r="T40" s="1">
-        <v>0</v>
-      </c>
-      <c r="U40" s="1">
-        <v>0</v>
-      </c>
-      <c r="V40" s="2">
-        <v>1</v>
-      </c>
-      <c r="W40" s="1">
-        <v>0</v>
-      </c>
-      <c r="X40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="1">
+      <c r="O40" s="3">
+        <v>0</v>
+      </c>
+      <c r="P40" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>0</v>
+      </c>
+      <c r="R40" s="3">
+        <v>0</v>
+      </c>
+      <c r="S40" s="3">
+        <v>0</v>
+      </c>
+      <c r="T40" s="3">
+        <v>0</v>
+      </c>
+      <c r="U40" s="3">
+        <v>0</v>
+      </c>
+      <c r="V40" s="3">
+        <v>1</v>
+      </c>
+      <c r="W40" s="3">
+        <v>0</v>
+      </c>
+      <c r="X40" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="3">
         <v>89.150001525878906</v>
       </c>
-      <c r="AA40">
+      <c r="AA40" s="4">
         <f t="shared" si="0"/>
         <v>263.65000152587891</v>
       </c>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB40" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -4377,8 +4540,11 @@
         <f t="shared" si="0"/>
         <v>263</v>
       </c>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -4461,8 +4627,11 @@
         <f t="shared" si="0"/>
         <v>262</v>
       </c>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -4545,8 +4714,11 @@
         <f t="shared" si="0"/>
         <v>261</v>
       </c>
-    </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -4629,8 +4801,11 @@
         <f t="shared" si="0"/>
         <v>260</v>
       </c>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -4713,8 +4888,11 @@
         <f t="shared" si="0"/>
         <v>259.25</v>
       </c>
-    </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AB45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -4798,7 +4976,7 @@
         <v>258.75</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>-0.29742455482482899</v>
       </c>
@@ -4882,7 +5060,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>-0.29742455482482899</v>
       </c>
